--- a/aq_files/0271.xlsx
+++ b/aq_files/0271.xlsx
@@ -2,12 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessment" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,10 +16,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -34,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,15 +49,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,346 +438,423 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Module: SQL Administrator</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Problem / Question</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Topic:</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Backup and Restore</t>
+          <t>break does:</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A) Exit loop B) Skip C) Continue D) None</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>continue does:</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A) Skip iteration B) Exit C) Stop D) None</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Q.No</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Output?
+for i in range(5):
+ if i==3: break
+ print(i)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Scenario-Based Question</t>
+          <t>A) 0 1 2 B) 0-4 C) Error D) None</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Output?
+for i in range(5):
+ if i==3: continue
+ print(i)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Write a MySQL command to create a backup of a database using mysqldump.</t>
+          <t>A) 0 1 2 4 B) All C) Error D) None</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>break works in:</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A company wants to perform a full database backup daily. Write the command and explain scheduling.</t>
+          <t>A) Loop B) Function C) Class D) None</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>3</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Two sum problem (find pair equals target).</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Write a MySQL command to restore a database from a backup file.</t>
+          <t>LeetCode-style problem (solve in code)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>4</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Find first unique character.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A database backup file needs to be restored to a new database. Write the SQL command.</t>
+          <t>LeetCode-style problem (solve in code)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>5</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Search element and break.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Explain difference between full backup and incremental backup with examples.</t>
+          <t>LeetCode-style problem (solve in code)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>6</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Skip negative numbers.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A production database crashed. Explain step-by-step how you would restore it.</t>
+          <t>LeetCode-style problem (solve in code)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>7</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Stop loop when sum exceeds limit.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Write a command to backup only specific tables.</t>
+          <t>LeetCode-style problem (solve in code)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>8</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Find first prime in range.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Explain importance of regular backups in production systems.</t>
+          <t>LeetCode-style problem (solve in code)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>9</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Skip vowels in string.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Design a backup strategy for an e-commerce platform.</t>
+          <t>LeetCode-style problem (solve in code)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>10</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Break when input equals 0.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Write command to restore backup into existing database.</t>
+          <t>LeetCode-style problem (solve in code)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>11</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Find first duplicate.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Explain how to verify backup integrity.</t>
+          <t>LeetCode-style problem (solve in code)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>12</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Skip spaces in string.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Explain point-in-time recovery with example.</t>
+          <t>LeetCode-style problem (solve in code)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>13</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Stop at first multiple of 7.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A developer accidentally deleted data. How would backup help?</t>
+          <t>LeetCode-style problem (solve in code)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>14</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Infinite loop with break.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Write command to backup database with compression.</t>
+          <t>LeetCode-style problem (solve in code)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>15</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Find first even number.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Explain risks of not maintaining backups.</t>
+          <t>LeetCode-style problem (solve in code)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>16</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Find index of first match.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Explain difference between logical and physical backups.</t>
+          <t>LeetCode-style problem (solve in code)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>17</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Break nested loops condition.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Write restore command using SQL dump file.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Explain automated backup scheduling using cron.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Explain recovery process after system failure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Hard</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Design disaster recovery strategy using backups.</t>
+          <t>LeetCode-style problem (solve in code)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>